--- a/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20251107.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20251107.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>22879</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pie Tin - 6"</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>150.98</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>150.98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
